--- a/explorations/step3result.xlsx
+++ b/explorations/step3result.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>'Autoimmune Disorders'</t>
+          <t>'Neurological Disorders', 'Autoimmune Disorders'</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>'Neurological Disorders'</t>
+          <t>'Autoimmune Disorders'</t>
         </is>
       </c>
     </row>
